--- a/ig/DM-AVRIL-2025/CodeSystem-tre-r389-statut-bilan-projet-personnalise.xlsx
+++ b/ig/DM-AVRIL-2025/CodeSystem-tre-r389-statut-bilan-projet-personnalise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -149,6 +149,36 @@
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>Statut d'un code concept</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date de dépréciation du code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date de retrait du code</t>
   </si>
   <si>
     <t>Level</t>
@@ -482,7 +512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -532,6 +562,48 @@
         <v>44</v>
       </c>
       <c r="D4" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -547,51 +619,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2"/>
     </row>
